--- a/p6_deployment/data/spain/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/p6_deployment/data/spain/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1638"/>
+  <dimension ref="A1:C1652"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25002,6 +25002,230 @@
         <v>315</v>
       </c>
     </row>
+    <row r="1639">
+      <c r="A1639" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1639" t="inlineStr">
+        <is>
+          <t xml:space="preserve">diaz de mera i 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1639" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="1640">
+      <c r="A1640" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1640" t="inlineStr">
+        <is>
+          <t xml:space="preserve">munuera montero j 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1640" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="1641">
+      <c r="A1641" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1641" t="inlineStr">
+        <is>
+          <t xml:space="preserve">alvendiz l 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1641" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="1642">
+      <c r="A1642" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1642" t="inlineStr">
+        <is>
+          <t xml:space="preserve">maeso f 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1642" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="1643">
+      <c r="A1643" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1643" t="inlineStr">
+        <is>
+          <t xml:space="preserve">ruiz a 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1643" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="1644">
+      <c r="A1644" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1644" t="inlineStr">
+        <is>
+          <t xml:space="preserve">garcia v 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1644" t="n">
+        <v>117</v>
+      </c>
+    </row>
+    <row r="1645">
+      <c r="A1645" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1645" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadi mallorca son moix
+  palma de mallorca </t>
+        </is>
+      </c>
+      <c r="C1645" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="1646">
+      <c r="A1646" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1646" t="inlineStr">
+        <is>
+          <t xml:space="preserve">reale arena
+  san sebastian </t>
+        </is>
+      </c>
+      <c r="C1646" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="1647">
+      <c r="A1647" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1647" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de mestalla
+  valencia </t>
+        </is>
+      </c>
+      <c r="C1647" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="1648">
+      <c r="A1648" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1648" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio el sadar
+  pamplona </t>
+        </is>
+      </c>
+      <c r="C1648" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="1649">
+      <c r="A1649" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1649" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de gran canaria
+  las palmas </t>
+        </is>
+      </c>
+      <c r="C1649" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="1650">
+      <c r="A1650" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1650" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de balaidos
+  vigo </t>
+        </is>
+      </c>
+      <c r="C1650" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="1651">
+      <c r="A1651" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1651" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio benito villamarin
+  sevilla </t>
+        </is>
+      </c>
+      <c r="C1651" t="n">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="1652">
+      <c r="A1652" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1652" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio san mames
+  bilbao </t>
+        </is>
+      </c>
+      <c r="C1652" t="n">
+        <v>165</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/spain/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/p6_deployment/data/spain/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1652"/>
+  <dimension ref="A1:C1658"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25226,6 +25226,92 @@
         <v>165</v>
       </c>
     </row>
+    <row r="1653">
+      <c r="A1653" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1653" t="inlineStr">
+        <is>
+          <t xml:space="preserve">sanchez j 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1653" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="1654">
+      <c r="A1654" t="inlineStr">
+        <is>
+          <t>referee</t>
+        </is>
+      </c>
+      <c r="B1654" t="inlineStr">
+        <is>
+          <t xml:space="preserve">vega a  c 
+  esp </t>
+        </is>
+      </c>
+      <c r="C1654" t="n">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="1655">
+      <c r="A1655" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1655" t="inlineStr"/>
+      <c r="C1655" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="1656">
+      <c r="A1656" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1656" t="inlineStr"/>
+      <c r="C1656" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="1657">
+      <c r="A1657" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1657" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio de la ceramica
+  villarreal </t>
+        </is>
+      </c>
+      <c r="C1657" t="n">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="1658">
+      <c r="A1658" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1658" t="inlineStr">
+        <is>
+          <t xml:space="preserve">estadio jose zorrilla
+  valladolid </t>
+        </is>
+      </c>
+      <c r="C1658" t="n">
+        <v>166</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/spain/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/p6_deployment/data/spain/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1658"/>
+  <dimension ref="A1:C1660"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25312,6 +25312,28 @@
         <v>166</v>
       </c>
     </row>
+    <row r="1659">
+      <c r="A1659" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1659" t="inlineStr"/>
+      <c r="C1659" t="n">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="1660">
+      <c r="A1660" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1660" t="inlineStr"/>
+      <c r="C1660" t="n">
+        <v>167</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/p6_deployment/data/spain/data_preparation/df_etiquetas_actualizado.xlsx
+++ b/p6_deployment/data/spain/data_preparation/df_etiquetas_actualizado.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C1660"/>
+  <dimension ref="A1:C1662"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -25334,6 +25334,28 @@
         <v>167</v>
       </c>
     </row>
+    <row r="1661">
+      <c r="A1661" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1661" t="inlineStr"/>
+      <c r="C1661" t="n">
+        <v>168</v>
+      </c>
+    </row>
+    <row r="1662">
+      <c r="A1662" t="inlineStr">
+        <is>
+          <t>venue</t>
+        </is>
+      </c>
+      <c r="B1662" t="inlineStr"/>
+      <c r="C1662" t="n">
+        <v>168</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
